--- a/data/source-data/GEOMIND-R-source-data.xlsx
+++ b/data/source-data/GEOMIND-R-source-data.xlsx
@@ -544,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO55"/>
+  <dimension ref="A1:AQ74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,110 +645,120 @@
       </c>
       <c r="T1" t="inlineStr">
         <is>
+          <t>bet_m2_g</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
           <t>si_al</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>na_al</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>k_al</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>ca_al</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>precursor</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>activator</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>activator_molarity</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ca_si_al</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
         <is>
           <t>q4_4al_pct</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>q4_3al_pct</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>q4_2al_pct</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>q4_1al_pct</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>q4_0al_pct</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>si_al_nmr</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>ari</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>al_iv_pct</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>cn_sr_exafs</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>chemical_shift_ppm</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>provenance_doi</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>source_label</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>leach_state</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>from_figure</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>value_repeated</t>
         </is>
@@ -808,23 +818,23 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="n">
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="n">
         <v>2.7</v>
       </c>
-      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr">
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>sodium_silicate</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
@@ -835,25 +845,27 @@
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr">
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr">
         <is>
           <t>10.1016/j.cemconres.2026.108214</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>kim2026</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>pre</t>
         </is>
       </c>
-      <c r="AN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="b">
+      <c r="AP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -911,23 +923,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="n">
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="n">
         <v>2.7</v>
       </c>
-      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr">
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>sodium_silicate</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
@@ -938,25 +950,27 @@
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr">
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr">
         <is>
           <t>10.1016/j.cemconres.2026.108214</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>kim2026</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>pre</t>
         </is>
       </c>
-      <c r="AN3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="b">
+      <c r="AP3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1014,23 +1028,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="n">
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="n">
         <v>2.7</v>
       </c>
-      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr">
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>sodium_silicate</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -1039,29 +1053,31 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="n">
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="n">
         <v>7.87</v>
       </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr">
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr">
         <is>
           <t>10.1016/j.cemconres.2026.108214</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>kim2026</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>pre</t>
         </is>
       </c>
-      <c r="AN4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="b">
+      <c r="AP4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1119,23 +1135,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="n">
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="n">
         <v>2.7</v>
       </c>
-      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr">
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>potassium_silicate</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
@@ -1146,25 +1162,27 @@
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr">
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
         <is>
           <t>10.1016/j.cemconres.2026.108214</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>kim2026</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>pre</t>
         </is>
       </c>
-      <c r="AN5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="b">
+      <c r="AP5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1222,23 +1240,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="n">
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="n">
         <v>2.7</v>
       </c>
-      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr">
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>potassium_silicate</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
@@ -1249,25 +1267,27 @@
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr">
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
         <is>
           <t>10.1016/j.cemconres.2026.108214</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>kim2026</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>pre</t>
         </is>
       </c>
-      <c r="AN6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="b">
+      <c r="AP6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1325,23 +1345,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="n">
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="n">
         <v>2.7</v>
       </c>
-      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr">
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>potassium_silicate</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
@@ -1350,29 +1370,31 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="n">
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="n">
         <v>7.55</v>
       </c>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr">
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
         <is>
           <t>10.1016/j.cemconres.2026.108214</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>kim2026</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>pre</t>
         </is>
       </c>
-      <c r="AN7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="b">
+      <c r="AP7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1424,66 +1446,68 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
-      <c r="T8" t="n">
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="n">
         <v>3</v>
       </c>
-      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr">
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>potassium_silicate</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="n">
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="n">
         <v>23.9</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AD8" t="n">
         <v>38.6</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AE8" t="n">
         <v>32.1</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AF8" t="n">
         <v>5.4</v>
       </c>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="n">
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="n">
         <v>1.42</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
         <v>2.81</v>
       </c>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="n">
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="n">
         <v>-88.5</v>
       </c>
-      <c r="AK8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>10.1039/d5ta90211h</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>nevin2026</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>pre</t>
         </is>
       </c>
-      <c r="AN8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="b">
+      <c r="AP8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1543,66 +1567,68 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
-      <c r="T9" t="n">
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr">
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>potassium_silicate</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="n">
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="n">
         <v>18.2</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AD9" t="n">
         <v>44.3</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AE9" t="n">
         <v>31.8</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AF9" t="n">
         <v>5.7</v>
       </c>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="n">
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="n">
         <v>1.45</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AI9" t="n">
         <v>2.75</v>
       </c>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="n">
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="n">
         <v>-89</v>
       </c>
-      <c r="AK9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>10.1039/d5ta90211h</t>
         </is>
       </c>
-      <c r="AL9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>nevin2026</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>pre</t>
         </is>
       </c>
-      <c r="AN9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="b">
+      <c r="AP9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1662,66 +1688,68 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="n">
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr">
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>potassium_silicate</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="n">
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="n">
         <v>17.3</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AD10" t="n">
         <v>47.4</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AE10" t="n">
         <v>33.1</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AF10" t="n">
         <v>2.3</v>
       </c>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="n">
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="n">
         <v>1.43</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AI10" t="n">
         <v>2.799</v>
       </c>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="n">
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="n">
         <v>-89</v>
       </c>
-      <c r="AK10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>10.1039/d5ta90211h</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>nevin2026</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>pre</t>
         </is>
       </c>
-      <c r="AN10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="b">
+      <c r="AP10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1781,66 +1809,68 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="n">
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="n">
         <v>3</v>
       </c>
-      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr">
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>potassium_silicate</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="n">
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="n">
         <v>21.3</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AD11" t="n">
         <v>36.1</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AE11" t="n">
         <v>37.7</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AF11" t="n">
         <v>4.9</v>
       </c>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="n">
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="n">
         <v>1.46</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AI11" t="n">
         <v>2.738</v>
       </c>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="n">
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="n">
         <v>-88.5</v>
       </c>
-      <c r="AK11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>10.1039/d5ta90211h</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>nevin2026</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
         <is>
           <t>pre</t>
         </is>
       </c>
-      <c r="AN11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="b">
+      <c r="AP11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1900,66 +1930,68 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
-      <c r="T12" t="n">
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="n">
         <v>3</v>
       </c>
-      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr">
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>potassium_silicate</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="n">
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="n">
         <v>26.5</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AD12" t="n">
         <v>38.1</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AE12" t="n">
         <v>29.9</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AF12" t="n">
         <v>5.4</v>
       </c>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="n">
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="n">
         <v>1.4</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AI12" t="n">
         <v>2.855</v>
       </c>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="n">
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="n">
         <v>-88.5</v>
       </c>
-      <c r="AK12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>10.1039/d5ta90211h</t>
         </is>
       </c>
-      <c r="AL12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>nevin2026</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
         <is>
           <t>pre</t>
         </is>
       </c>
-      <c r="AN12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="b">
+      <c r="AP12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2011,66 +2043,68 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="n">
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="n">
         <v>3</v>
       </c>
-      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr">
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>potassium_silicate</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="n">
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="n">
         <v>21.7</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AD13" t="n">
         <v>41.7</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AE13" t="n">
         <v>32.5</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AF13" t="n">
         <v>4.2</v>
       </c>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="n">
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="n">
         <v>1.42</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AI13" t="n">
         <v>2.810999999999999</v>
       </c>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="n">
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="n">
         <v>-88.5</v>
       </c>
-      <c r="AK13" t="inlineStr">
+      <c r="AM13" t="inlineStr">
         <is>
           <t>10.1039/d5ta90211h</t>
         </is>
       </c>
-      <c r="AL13" t="inlineStr">
+      <c r="AN13" t="inlineStr">
         <is>
           <t>nevin2026</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
+      <c r="AO13" t="inlineStr">
         <is>
           <t>post</t>
         </is>
       </c>
-      <c r="AN13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="b">
+      <c r="AP13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2122,66 +2156,68 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="n">
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="n">
         <v>3</v>
       </c>
-      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr">
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>potassium_silicate</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>32.1</v>
-      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
         <v>32.1</v>
       </c>
       <c r="AD14" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="AF14" t="n">
         <v>3.8</v>
       </c>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="n">
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="n">
         <v>1.37</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AI14" t="n">
         <v>2.927</v>
       </c>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="n">
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="n">
         <v>-89</v>
       </c>
-      <c r="AK14" t="inlineStr">
+      <c r="AM14" t="inlineStr">
         <is>
           <t>10.1039/d5ta90211h</t>
         </is>
       </c>
-      <c r="AL14" t="inlineStr">
+      <c r="AN14" t="inlineStr">
         <is>
           <t>nevin2026</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
+      <c r="AO14" t="inlineStr">
         <is>
           <t>post</t>
         </is>
       </c>
-      <c r="AN14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="b">
+      <c r="AP14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2233,66 +2269,68 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
-      <c r="T15" t="n">
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="n">
         <v>3</v>
       </c>
-      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr">
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>potassium_silicate</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="n">
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="n">
         <v>24.6</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AD15" t="n">
         <v>37.3</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AE15" t="n">
         <v>32.8</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AF15" t="n">
         <v>5.3</v>
       </c>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="n">
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="n">
         <v>1.42</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AI15" t="n">
         <v>2.812</v>
       </c>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="n">
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="n">
         <v>-89</v>
       </c>
-      <c r="AK15" t="inlineStr">
+      <c r="AM15" t="inlineStr">
         <is>
           <t>10.1039/d5ta90211h</t>
         </is>
       </c>
-      <c r="AL15" t="inlineStr">
+      <c r="AN15" t="inlineStr">
         <is>
           <t>nevin2026</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
+      <c r="AO15" t="inlineStr">
         <is>
           <t>post</t>
         </is>
       </c>
-      <c r="AN15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="b">
+      <c r="AP15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2344,66 +2382,68 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="n">
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr">
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>potassium_silicate</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="n">
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="n">
         <v>19.2</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AD16" t="n">
         <v>46</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AE16" t="n">
         <v>30.5</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AF16" t="n">
         <v>4.2</v>
       </c>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="n">
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="n">
         <v>1.43</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AI16" t="n">
         <v>2.8</v>
       </c>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="n">
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="n">
         <v>-88.5</v>
       </c>
-      <c r="AK16" t="inlineStr">
+      <c r="AM16" t="inlineStr">
         <is>
           <t>10.1039/d5ta90211h</t>
         </is>
       </c>
-      <c r="AL16" t="inlineStr">
+      <c r="AN16" t="inlineStr">
         <is>
           <t>nevin2026</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
+      <c r="AO16" t="inlineStr">
         <is>
           <t>post</t>
         </is>
       </c>
-      <c r="AN16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="b">
+      <c r="AP16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2455,66 +2495,68 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
-      <c r="T17" t="n">
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="n">
         <v>3</v>
       </c>
-      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr">
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>potassium_silicate</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="n">
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="n">
         <v>21.9</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AD17" t="n">
         <v>38.8</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AE17" t="n">
         <v>32.5</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AF17" t="n">
         <v>6.8</v>
       </c>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="n">
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="n">
         <v>1.45</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AI17" t="n">
         <v>2.758</v>
       </c>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="n">
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="n">
         <v>-88.5</v>
       </c>
-      <c r="AK17" t="inlineStr">
+      <c r="AM17" t="inlineStr">
         <is>
           <t>10.1039/d5ta90211h</t>
         </is>
       </c>
-      <c r="AL17" t="inlineStr">
+      <c r="AN17" t="inlineStr">
         <is>
           <t>nevin2026</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
+      <c r="AO17" t="inlineStr">
         <is>
           <t>post</t>
         </is>
       </c>
-      <c r="AN17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="b">
+      <c r="AP17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2578,17 +2620,17 @@
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr">
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>K2O</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
@@ -2599,25 +2641,27 @@
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr">
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr">
         <is>
           <t>10.1617/s11527-021-01758-y</t>
         </is>
       </c>
-      <c r="AL18" t="inlineStr">
+      <c r="AN18" t="inlineStr">
         <is>
           <t>kurumisawa2021</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
+      <c r="AO18" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO18" t="b">
+      <c r="AP18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2681,17 +2725,17 @@
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr">
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>K2O</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
@@ -2702,25 +2746,27 @@
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr">
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr">
         <is>
           <t>10.1617/s11527-021-01758-y</t>
         </is>
       </c>
-      <c r="AL19" t="inlineStr">
+      <c r="AN19" t="inlineStr">
         <is>
           <t>kurumisawa2021</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
+      <c r="AO19" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO19" t="b">
+      <c r="AP19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ19" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2784,17 +2830,17 @@
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr">
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>K2O</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
@@ -2805,25 +2851,27 @@
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr">
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr">
         <is>
           <t>10.1617/s11527-021-01758-y</t>
         </is>
       </c>
-      <c r="AL20" t="inlineStr">
+      <c r="AN20" t="inlineStr">
         <is>
           <t>kurumisawa2021</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
+      <c r="AO20" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO20" t="b">
+      <c r="AP20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ20" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2887,17 +2935,17 @@
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr">
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>K2O</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
@@ -2908,25 +2956,27 @@
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr">
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr">
         <is>
           <t>10.1617/s11527-021-01758-y</t>
         </is>
       </c>
-      <c r="AL21" t="inlineStr">
+      <c r="AN21" t="inlineStr">
         <is>
           <t>kurumisawa2021</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
+      <c r="AO21" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO21" t="b">
+      <c r="AP21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ21" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2990,17 +3040,17 @@
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr">
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>K2O</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
@@ -3011,25 +3061,27 @@
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr">
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr">
         <is>
           <t>10.1617/s11527-021-01758-y</t>
         </is>
       </c>
-      <c r="AL22" t="inlineStr">
+      <c r="AN22" t="inlineStr">
         <is>
           <t>kurumisawa2021</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
+      <c r="AO22" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO22" t="b">
+      <c r="AP22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ22" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3093,17 +3145,17 @@
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr">
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>K2O</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
@@ -3114,25 +3166,27 @@
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr">
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr">
         <is>
           <t>10.1617/s11527-021-01758-y</t>
         </is>
       </c>
-      <c r="AL23" t="inlineStr">
+      <c r="AN23" t="inlineStr">
         <is>
           <t>kurumisawa2021</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
+      <c r="AO23" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO23" t="b">
+      <c r="AP23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ23" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3196,17 +3250,17 @@
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr">
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>Na2O</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
@@ -3217,25 +3271,27 @@
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr">
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr">
         <is>
           <t>10.1617/s11527-021-01758-y</t>
         </is>
       </c>
-      <c r="AL24" t="inlineStr">
+      <c r="AN24" t="inlineStr">
         <is>
           <t>kurumisawa2021</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
+      <c r="AO24" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO24" t="b">
+      <c r="AP24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ24" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3299,17 +3355,17 @@
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr">
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>Na2O</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
@@ -3320,25 +3376,27 @@
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr">
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr">
         <is>
           <t>10.1617/s11527-021-01758-y</t>
         </is>
       </c>
-      <c r="AL25" t="inlineStr">
+      <c r="AN25" t="inlineStr">
         <is>
           <t>kurumisawa2021</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
+      <c r="AO25" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO25" t="b">
+      <c r="AP25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ25" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3402,17 +3460,17 @@
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr">
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>0.5K2O+0.5Na2O</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
@@ -3423,25 +3481,27 @@
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="inlineStr">
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr">
         <is>
           <t>10.1617/s11527-021-01758-y</t>
         </is>
       </c>
-      <c r="AL26" t="inlineStr">
+      <c r="AN26" t="inlineStr">
         <is>
           <t>kurumisawa2021</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
+      <c r="AO26" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO26" t="b">
+      <c r="AP26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3505,17 +3565,17 @@
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr">
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>0.5K2O+0.5Na2O</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
@@ -3526,25 +3586,27 @@
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr">
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr">
         <is>
           <t>10.1617/s11527-021-01758-y</t>
         </is>
       </c>
-      <c r="AL27" t="inlineStr">
+      <c r="AN27" t="inlineStr">
         <is>
           <t>kurumisawa2021</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
+      <c r="AO27" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO27" t="b">
+      <c r="AP27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ27" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3610,17 +3672,17 @@
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr">
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr">
         <is>
           <t>fly_ash</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>NaOH_sodium_silicate</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
@@ -3631,25 +3693,27 @@
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr">
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr">
         <is>
           <t>10.1016/j.jhazmat.2016.07.003</t>
         </is>
       </c>
-      <c r="AL28" t="inlineStr">
+      <c r="AN28" t="inlineStr">
         <is>
           <t>jang2016</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
+      <c r="AO28" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO28" t="b">
+      <c r="AP28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3715,17 +3779,17 @@
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr">
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr">
         <is>
           <t>fly_ash</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>NaOH_sodium_silicate</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
@@ -3736,25 +3800,27 @@
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr">
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr">
         <is>
           <t>10.1016/j.jhazmat.2016.07.003</t>
         </is>
       </c>
-      <c r="AL29" t="inlineStr">
+      <c r="AN29" t="inlineStr">
         <is>
           <t>jang2016</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
+      <c r="AO29" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO29" t="b">
+      <c r="AP29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3820,17 +3886,17 @@
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr">
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr">
         <is>
           <t>fly_ash</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>NaOH_sodium_silicate</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
@@ -3841,25 +3907,27 @@
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr">
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr">
         <is>
           <t>10.1016/j.jhazmat.2016.07.003</t>
         </is>
       </c>
-      <c r="AL30" t="inlineStr">
+      <c r="AN30" t="inlineStr">
         <is>
           <t>jang2016</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
+      <c r="AO30" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="b">
+      <c r="AP30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3925,17 +3993,17 @@
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr">
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr">
         <is>
           <t>fly_ash</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>NaOH_sodium_silicate</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
@@ -3946,25 +4014,27 @@
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr"/>
-      <c r="AK31" t="inlineStr">
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr">
         <is>
           <t>10.1016/j.jhazmat.2016.07.003</t>
         </is>
       </c>
-      <c r="AL31" t="inlineStr">
+      <c r="AN31" t="inlineStr">
         <is>
           <t>jang2016</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
+      <c r="AO31" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO31" t="b">
+      <c r="AP31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4030,17 +4100,17 @@
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr">
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr">
         <is>
           <t>fly_ash</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>NaOH_sodium_silicate</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
@@ -4051,25 +4121,27 @@
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="inlineStr">
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr">
         <is>
           <t>10.1016/j.jhazmat.2016.07.003</t>
         </is>
       </c>
-      <c r="AL32" t="inlineStr">
+      <c r="AN32" t="inlineStr">
         <is>
           <t>jang2016</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
+      <c r="AO32" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO32" t="b">
+      <c r="AP32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4135,17 +4207,17 @@
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr">
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr">
         <is>
           <t>fly_ash</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>NaOH_sodium_silicate</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
@@ -4156,25 +4228,27 @@
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="inlineStr">
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr">
         <is>
           <t>10.1016/j.jhazmat.2016.07.003</t>
         </is>
       </c>
-      <c r="AL33" t="inlineStr">
+      <c r="AN33" t="inlineStr">
         <is>
           <t>jang2016</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
+      <c r="AO33" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO33" t="b">
+      <c r="AP33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4240,17 +4314,17 @@
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr">
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr">
         <is>
           <t>fly_ash_slag</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>NaOH_sodium_silicate</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr"/>
@@ -4261,25 +4335,27 @@
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="inlineStr">
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr">
         <is>
           <t>10.1016/j.jhazmat.2016.07.003</t>
         </is>
       </c>
-      <c r="AL34" t="inlineStr">
+      <c r="AN34" t="inlineStr">
         <is>
           <t>jang2016</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
+      <c r="AO34" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO34" t="b">
+      <c r="AP34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4345,17 +4421,17 @@
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr">
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr">
         <is>
           <t>fly_ash_slag</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>NaOH_sodium_silicate</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
@@ -4366,25 +4442,27 @@
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="inlineStr"/>
-      <c r="AK35" t="inlineStr">
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr">
         <is>
           <t>10.1016/j.jhazmat.2016.07.003</t>
         </is>
       </c>
-      <c r="AL35" t="inlineStr">
+      <c r="AN35" t="inlineStr">
         <is>
           <t>jang2016</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
+      <c r="AO35" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO35" t="b">
+      <c r="AP35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4450,17 +4528,17 @@
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr">
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr">
         <is>
           <t>fly_ash_slag</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>NaOH_sodium_silicate</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
@@ -4471,25 +4549,27 @@
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="inlineStr"/>
       <c r="AJ36" t="inlineStr"/>
-      <c r="AK36" t="inlineStr">
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr">
         <is>
           <t>10.1016/j.jhazmat.2016.07.003</t>
         </is>
       </c>
-      <c r="AL36" t="inlineStr">
+      <c r="AN36" t="inlineStr">
         <is>
           <t>jang2016</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
+      <c r="AO36" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO36" t="b">
+      <c r="AP36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4555,17 +4635,17 @@
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr">
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr">
         <is>
           <t>fly_ash_slag</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>NaOH_sodium_silicate</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
@@ -4576,25 +4656,27 @@
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="inlineStr"/>
       <c r="AJ37" t="inlineStr"/>
-      <c r="AK37" t="inlineStr">
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr">
         <is>
           <t>10.1016/j.jhazmat.2016.07.003</t>
         </is>
       </c>
-      <c r="AL37" t="inlineStr">
+      <c r="AN37" t="inlineStr">
         <is>
           <t>jang2016</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
+      <c r="AO37" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO37" t="b">
+      <c r="AP37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4660,17 +4742,17 @@
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr">
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr">
         <is>
           <t>fly_ash_slag</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>NaOH_sodium_silicate</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
@@ -4681,25 +4763,27 @@
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr"/>
-      <c r="AK38" t="inlineStr">
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr">
         <is>
           <t>10.1016/j.jhazmat.2016.07.003</t>
         </is>
       </c>
-      <c r="AL38" t="inlineStr">
+      <c r="AN38" t="inlineStr">
         <is>
           <t>jang2016</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
+      <c r="AO38" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO38" t="b">
+      <c r="AP38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4765,17 +4849,17 @@
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr">
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr">
         <is>
           <t>fly_ash_slag</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>NaOH_sodium_silicate</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
@@ -4786,25 +4870,27 @@
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr"/>
-      <c r="AK39" t="inlineStr">
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr">
         <is>
           <t>10.1016/j.jhazmat.2016.07.003</t>
         </is>
       </c>
-      <c r="AL39" t="inlineStr">
+      <c r="AN39" t="inlineStr">
         <is>
           <t>jang2016</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
+      <c r="AO39" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO39" t="b">
+      <c r="AP39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4870,12 +4956,12 @@
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr">
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr">
         <is>
           <t>portland_cement</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr"/>
@@ -4887,25 +4973,27 @@
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="inlineStr"/>
       <c r="AJ40" t="inlineStr"/>
-      <c r="AK40" t="inlineStr">
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr">
         <is>
           <t>10.1016/j.jhazmat.2016.07.003</t>
         </is>
       </c>
-      <c r="AL40" t="inlineStr">
+      <c r="AN40" t="inlineStr">
         <is>
           <t>jang2016</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
+      <c r="AO40" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO40" t="b">
+      <c r="AP40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4971,12 +5059,12 @@
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr">
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr">
         <is>
           <t>portland_cement</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="inlineStr"/>
@@ -4988,25 +5076,27 @@
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="inlineStr"/>
       <c r="AJ41" t="inlineStr"/>
-      <c r="AK41" t="inlineStr">
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr">
         <is>
           <t>10.1016/j.jhazmat.2016.07.003</t>
         </is>
       </c>
-      <c r="AL41" t="inlineStr">
+      <c r="AN41" t="inlineStr">
         <is>
           <t>jang2016</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
+      <c r="AO41" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO41" t="b">
+      <c r="AP41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5068,17 +5158,17 @@
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr">
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr">
         <is>
           <t>fly_ash</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>sodium_silicate</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr"/>
@@ -5089,25 +5179,27 @@
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="inlineStr"/>
       <c r="AJ42" t="inlineStr"/>
-      <c r="AK42" t="inlineStr">
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr">
         <is>
           <t>10.1016/j.conbuildmat.2025.144217</t>
         </is>
       </c>
-      <c r="AL42" t="inlineStr">
+      <c r="AN42" t="inlineStr">
         <is>
           <t>stanojevic2025</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
+      <c r="AO42" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO42" t="b">
+      <c r="AP42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ42" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5169,17 +5261,17 @@
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr">
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr">
         <is>
           <t>fly_ash</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>sodium_silicate</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr"/>
@@ -5190,25 +5282,27 @@
       <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="inlineStr"/>
       <c r="AJ43" t="inlineStr"/>
-      <c r="AK43" t="inlineStr">
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr">
         <is>
           <t>10.1016/j.conbuildmat.2025.144217</t>
         </is>
       </c>
-      <c r="AL43" t="inlineStr">
+      <c r="AN43" t="inlineStr">
         <is>
           <t>stanojevic2025</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
+      <c r="AO43" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO43" t="b">
+      <c r="AP43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ43" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5270,17 +5364,17 @@
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr">
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr">
         <is>
           <t>blast_furnace_slag</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>sodium_silicate</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr"/>
@@ -5291,25 +5385,27 @@
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="inlineStr"/>
-      <c r="AK44" t="inlineStr">
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr">
         <is>
           <t>10.1016/j.jhazmat.2019.121765</t>
         </is>
       </c>
-      <c r="AL44" t="inlineStr">
+      <c r="AN44" t="inlineStr">
         <is>
           <t>komljenovic2020</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
+      <c r="AO44" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO44" t="b">
+      <c r="AP44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ44" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5371,17 +5467,17 @@
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr">
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr">
         <is>
           <t>blast_furnace_slag</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>sodium_silicate</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr"/>
@@ -5392,25 +5488,27 @@
       <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="inlineStr"/>
       <c r="AJ45" t="inlineStr"/>
-      <c r="AK45" t="inlineStr">
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr">
         <is>
           <t>10.1016/j.jhazmat.2019.121765</t>
         </is>
       </c>
-      <c r="AL45" t="inlineStr">
+      <c r="AN45" t="inlineStr">
         <is>
           <t>komljenovic2020</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
+      <c r="AO45" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO45" t="b">
+      <c r="AP45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ45" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5466,23 +5564,23 @@
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
-      <c r="T46" t="n">
-        <v>1</v>
-      </c>
-      <c r="U46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="n">
+        <v>1</v>
+      </c>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr">
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>NaOH_CsOH</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr"/>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr"/>
@@ -5493,25 +5591,27 @@
       <c r="AH46" t="inlineStr"/>
       <c r="AI46" t="inlineStr"/>
       <c r="AJ46" t="inlineStr"/>
-      <c r="AK46" t="inlineStr">
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr">
         <is>
           <t>Arbel-Haddad 2022 J.Nucl.Mater 133Cs MK-geopolymer (DOI-unverified-AAM)</t>
         </is>
       </c>
-      <c r="AL46" t="inlineStr">
+      <c r="AN46" t="inlineStr">
         <is>
           <t>arbelhaddad2022</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
+      <c r="AO46" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO46" t="b">
+      <c r="AP46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ46" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5567,23 +5667,23 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
-      <c r="T47" t="n">
-        <v>1</v>
-      </c>
-      <c r="U47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr">
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>NaOH_CsOH</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr"/>
@@ -5594,25 +5694,27 @@
       <c r="AH47" t="inlineStr"/>
       <c r="AI47" t="inlineStr"/>
       <c r="AJ47" t="inlineStr"/>
-      <c r="AK47" t="inlineStr">
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr">
         <is>
           <t>Arbel-Haddad 2022 J.Nucl.Mater 133Cs MK-geopolymer (DOI-unverified-AAM)</t>
         </is>
       </c>
-      <c r="AL47" t="inlineStr">
+      <c r="AN47" t="inlineStr">
         <is>
           <t>arbelhaddad2022</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
+      <c r="AO47" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO47" t="b">
+      <c r="AP47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ47" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5668,23 +5770,23 @@
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
-      <c r="T48" t="n">
-        <v>1</v>
-      </c>
-      <c r="U48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
       <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr">
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>NaOH_CsOH</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr"/>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="inlineStr"/>
@@ -5695,25 +5797,27 @@
       <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="inlineStr"/>
       <c r="AJ48" t="inlineStr"/>
-      <c r="AK48" t="inlineStr">
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr">
         <is>
           <t>Arbel-Haddad 2022 J.Nucl.Mater 133Cs MK-geopolymer (DOI-unverified-AAM)</t>
         </is>
       </c>
-      <c r="AL48" t="inlineStr">
+      <c r="AN48" t="inlineStr">
         <is>
           <t>arbelhaddad2022</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
+      <c r="AO48" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO48" t="b">
+      <c r="AP48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ48" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5769,23 +5873,23 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
-      <c r="T49" t="n">
-        <v>1</v>
-      </c>
-      <c r="U49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="n">
+        <v>1</v>
+      </c>
       <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr">
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>NaOH_CsOH</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr"/>
@@ -5796,25 +5900,27 @@
       <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="inlineStr"/>
       <c r="AJ49" t="inlineStr"/>
-      <c r="AK49" t="inlineStr">
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr">
         <is>
           <t>Arbel-Haddad 2022 J.Nucl.Mater 133Cs MK-geopolymer (DOI-unverified-AAM)</t>
         </is>
       </c>
-      <c r="AL49" t="inlineStr">
+      <c r="AN49" t="inlineStr">
         <is>
           <t>arbelhaddad2022</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
+      <c r="AO49" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO49" t="b">
+      <c r="AP49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ49" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5870,23 +5976,23 @@
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
-      <c r="T50" t="n">
-        <v>1</v>
-      </c>
-      <c r="U50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="n">
+        <v>1</v>
+      </c>
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr">
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>NaOH_CsOH</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr"/>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr"/>
@@ -5897,25 +6003,27 @@
       <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="inlineStr"/>
       <c r="AJ50" t="inlineStr"/>
-      <c r="AK50" t="inlineStr">
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="inlineStr">
         <is>
           <t>Arbel-Haddad 2022 J.Nucl.Mater 133Cs MK-geopolymer (DOI-unverified-AAM)</t>
         </is>
       </c>
-      <c r="AL50" t="inlineStr">
+      <c r="AN50" t="inlineStr">
         <is>
           <t>arbelhaddad2022</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
+      <c r="AO50" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO50" t="b">
+      <c r="AP50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ50" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5971,23 +6079,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
-      <c r="T51" t="n">
-        <v>1</v>
-      </c>
-      <c r="U51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
       <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr">
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr">
         <is>
           <t>metakaolin</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>NaOH_CsOH</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr"/>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr"/>
@@ -5998,25 +6106,27 @@
       <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="inlineStr"/>
       <c r="AJ51" t="inlineStr"/>
-      <c r="AK51" t="inlineStr">
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr">
         <is>
           <t>Arbel-Haddad 2022 J.Nucl.Mater 133Cs MK-geopolymer (DOI-unverified-AAM)</t>
         </is>
       </c>
-      <c r="AL51" t="inlineStr">
+      <c r="AN51" t="inlineStr">
         <is>
           <t>arbelhaddad2022</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
+      <c r="AO51" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO51" t="b">
+      <c r="AP51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ51" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6074,17 +6184,17 @@
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr">
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr">
         <is>
           <t>metakaolin_blast_furnace_slag</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>sodium_silicate</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr"/>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="inlineStr"/>
@@ -6095,25 +6205,27 @@
       <c r="AH52" t="inlineStr"/>
       <c r="AI52" t="inlineStr"/>
       <c r="AJ52" t="inlineStr"/>
-      <c r="AK52" t="inlineStr">
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr">
         <is>
           <t>10.3390/su17041756</t>
         </is>
       </c>
-      <c r="AL52" t="inlineStr">
+      <c r="AN52" t="inlineStr">
         <is>
           <t>frederickx2025</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
+      <c r="AO52" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO52" t="b">
+      <c r="AP52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ52" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6171,17 +6283,17 @@
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr">
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr">
         <is>
           <t>metakaolin_blast_furnace_slag</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>sodium_silicate</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr"/>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr"/>
@@ -6192,25 +6304,27 @@
       <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="inlineStr"/>
       <c r="AJ53" t="inlineStr"/>
-      <c r="AK53" t="inlineStr">
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr">
         <is>
           <t>10.3390/su17041756</t>
         </is>
       </c>
-      <c r="AL53" t="inlineStr">
+      <c r="AN53" t="inlineStr">
         <is>
           <t>frederickx2025</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
+      <c r="AO53" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO53" t="b">
+      <c r="AP53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ53" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6268,17 +6382,17 @@
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr">
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr">
         <is>
           <t>metakaolin_blast_furnace_slag</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>sodium_silicate</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr"/>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="inlineStr"/>
@@ -6289,25 +6403,27 @@
       <c r="AH54" t="inlineStr"/>
       <c r="AI54" t="inlineStr"/>
       <c r="AJ54" t="inlineStr"/>
-      <c r="AK54" t="inlineStr">
+      <c r="AK54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="inlineStr">
         <is>
           <t>10.3390/su17041756</t>
         </is>
       </c>
-      <c r="AL54" t="inlineStr">
+      <c r="AN54" t="inlineStr">
         <is>
           <t>frederickx2025</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
+      <c r="AO54" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO54" t="b">
+      <c r="AP54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ54" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6365,17 +6481,17 @@
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr">
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr">
         <is>
           <t>metakaolin_blast_furnace_slag</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>sodium_silicate</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr"/>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr"/>
@@ -6386,25 +6502,2116 @@
       <c r="AH55" t="inlineStr"/>
       <c r="AI55" t="inlineStr"/>
       <c r="AJ55" t="inlineStr"/>
-      <c r="AK55" t="inlineStr">
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr">
         <is>
           <t>10.3390/su17041756</t>
         </is>
       </c>
-      <c r="AL55" t="inlineStr">
+      <c r="AN55" t="inlineStr">
         <is>
           <t>frederickx2025</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
+      <c r="AO55" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="AN55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO55" t="b">
+      <c r="AP55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>vandevenne2018_AAM_1_Cs</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>AAM_1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>slag_blend</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Cs</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="n">
+        <v>14</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>leached_pct</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>2</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>milli_q_water</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>28</v>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="n">
+        <v>363.15</v>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>synthetic_ca_si_al_slag</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>sodium_hydroxide</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>10.1016/j.jnucmat.2018.08.045</t>
+        </is>
+      </c>
+      <c r="AN56" t="inlineStr">
+        <is>
+          <t>vandevenne2018</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AP56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>vandevenne2018_AAM_1_Sr</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>AAM_1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>slag_blend</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Sr</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>leached_pct</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>milli_q_water</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>28</v>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="n">
+        <v>363.15</v>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>synthetic_ca_si_al_slag</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>sodium_hydroxide</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr"/>
+      <c r="AJ57" t="inlineStr"/>
+      <c r="AK57" t="inlineStr"/>
+      <c r="AL57" t="inlineStr"/>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>10.1016/j.jnucmat.2018.08.045</t>
+        </is>
+      </c>
+      <c r="AN57" t="inlineStr">
+        <is>
+          <t>vandevenne2018</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AP57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>vandevenne2018_AAM_1.1_Cs</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>AAM_1.1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>slag_blend</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Cs</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>leached_pct</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>milli_q_water</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>28</v>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="n">
+        <v>363.15</v>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>synthetic_ca_si_al_slag</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>sodium_hydroxide</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr"/>
+      <c r="AJ58" t="inlineStr"/>
+      <c r="AK58" t="inlineStr"/>
+      <c r="AL58" t="inlineStr"/>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>10.1016/j.jnucmat.2018.08.045</t>
+        </is>
+      </c>
+      <c r="AN58" t="inlineStr">
+        <is>
+          <t>vandevenne2018</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AP58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>vandevenne2018_AAM_1.1_Sr</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>AAM_1.1</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>slag_blend</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Sr</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>leached_pct</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>milli_q_water</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>28</v>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="n">
+        <v>363.15</v>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>synthetic_ca_si_al_slag</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>sodium_hydroxide</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AC59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr"/>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr"/>
+      <c r="AJ59" t="inlineStr"/>
+      <c r="AK59" t="inlineStr"/>
+      <c r="AL59" t="inlineStr"/>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>10.1016/j.jnucmat.2018.08.045</t>
+        </is>
+      </c>
+      <c r="AN59" t="inlineStr">
+        <is>
+          <t>vandevenne2018</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AP59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>vandevenne2018_AAM_2_Cs</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>AAM_2</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>slag_blend</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Cs</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>leached_pct</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>milli_q_water</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>28</v>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="n">
+        <v>363.15</v>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="n">
+        <v>2</v>
+      </c>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>synthetic_ca_si_al_slag</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>sodium_hydroxide</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr"/>
+      <c r="AJ60" t="inlineStr"/>
+      <c r="AK60" t="inlineStr"/>
+      <c r="AL60" t="inlineStr"/>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>10.1016/j.jnucmat.2018.08.045</t>
+        </is>
+      </c>
+      <c r="AN60" t="inlineStr">
+        <is>
+          <t>vandevenne2018</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AP60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>vandevenne2018_AAM_2_Sr</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>AAM_2</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>slag_blend</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Sr</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>leached_pct</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>milli_q_water</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>28</v>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="n">
+        <v>363.15</v>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="n">
+        <v>2</v>
+      </c>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>synthetic_ca_si_al_slag</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>sodium_hydroxide</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="inlineStr"/>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>10.1016/j.jnucmat.2018.08.045</t>
+        </is>
+      </c>
+      <c r="AN61" t="inlineStr">
+        <is>
+          <t>vandevenne2018</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AP61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>vandevenne2018_AAM_2.4_Cs</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>AAM_2.4</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>slag_blend</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Cs</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="n">
+        <v>40</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>leached_pct</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>2</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>milli_q_water</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>28</v>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="n">
+        <v>363.15</v>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>synthetic_ca_si_al_slag</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>sodium_hydroxide</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
+      <c r="AL62" t="inlineStr"/>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>10.1016/j.jnucmat.2018.08.045</t>
+        </is>
+      </c>
+      <c r="AN62" t="inlineStr">
+        <is>
+          <t>vandevenne2018</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AP62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>vandevenne2018_AAM_2.4_Sr</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>AAM_2.4</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>slag_blend</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Sr</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>leached_pct</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>milli_q_water</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>28</v>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="n">
+        <v>363.15</v>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>synthetic_ca_si_al_slag</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>sodium_hydroxide</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AC63" t="inlineStr"/>
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr"/>
+      <c r="AJ63" t="inlineStr"/>
+      <c r="AK63" t="inlineStr"/>
+      <c r="AL63" t="inlineStr"/>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>10.1016/j.jnucmat.2018.08.045</t>
+        </is>
+      </c>
+      <c r="AN63" t="inlineStr">
+        <is>
+          <t>vandevenne2018</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AP63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>vandevenne2018_AAM_3.4_Cs</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>AAM_3.4</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>slag_blend</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Cs</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" t="n">
+        <v>46</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>leached_pct</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>2</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>milli_q_water</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>28</v>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="n">
+        <v>363.15</v>
+      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>synthetic_ca_si_al_slag</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>sodium_hydroxide</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC64" t="inlineStr"/>
+      <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr"/>
+      <c r="AJ64" t="inlineStr"/>
+      <c r="AK64" t="inlineStr"/>
+      <c r="AL64" t="inlineStr"/>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>10.1016/j.jnucmat.2018.08.045</t>
+        </is>
+      </c>
+      <c r="AN64" t="inlineStr">
+        <is>
+          <t>vandevenne2018</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AP64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>vandevenne2018_AAM_3.4_Sr</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>AAM_3.4</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>slag_blend</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Sr</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>leached_pct</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>milli_q_water</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>28</v>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="n">
+        <v>363.15</v>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>synthetic_ca_si_al_slag</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>sodium_hydroxide</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC65" t="inlineStr"/>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr"/>
+      <c r="AJ65" t="inlineStr"/>
+      <c r="AK65" t="inlineStr"/>
+      <c r="AL65" t="inlineStr"/>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>10.1016/j.jnucmat.2018.08.045</t>
+        </is>
+      </c>
+      <c r="AN65" t="inlineStr">
+        <is>
+          <t>vandevenne2018</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AP65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>vandevenne2018_AAM_3.4b_Cs</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>AAM_3.4b</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>slag_blend</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Cs</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>leached_pct</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>milli_q_water</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>28</v>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="n">
+        <v>363.15</v>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>synthetic_ca_si_al_slag</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>sodium_hydroxide</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC66" t="inlineStr"/>
+      <c r="AD66" t="inlineStr"/>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr"/>
+      <c r="AJ66" t="inlineStr"/>
+      <c r="AK66" t="inlineStr"/>
+      <c r="AL66" t="inlineStr"/>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>10.1016/j.jnucmat.2018.08.045</t>
+        </is>
+      </c>
+      <c r="AN66" t="inlineStr">
+        <is>
+          <t>vandevenne2018</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AP66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ66" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>vandevenne2018_AAM_3.4b_Sr</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>AAM_3.4b</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>slag_blend</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Sr</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" t="n">
+        <v>5</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>leached_pct</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>milli_q_water</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>28</v>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="n">
+        <v>363.15</v>
+      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>synthetic_ca_si_al_slag</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>sodium_hydroxide</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr"/>
+      <c r="AJ67" t="inlineStr"/>
+      <c r="AK67" t="inlineStr"/>
+      <c r="AL67" t="inlineStr"/>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>10.1016/j.jnucmat.2018.08.045</t>
+        </is>
+      </c>
+      <c r="AN67" t="inlineStr">
+        <is>
+          <t>vandevenne2018</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AP67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ67" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>vandevenne2018_AAM_5.1_Cs</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>AAM_5.1</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>slag_blend</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Cs</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>leached_pct</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>milli_q_water</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>28</v>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="n">
+        <v>363.15</v>
+      </c>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>synthetic_ca_si_al_slag</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>sodium_hydroxide</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AC68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr"/>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr"/>
+      <c r="AJ68" t="inlineStr"/>
+      <c r="AK68" t="inlineStr"/>
+      <c r="AL68" t="inlineStr"/>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>10.1016/j.jnucmat.2018.08.045</t>
+        </is>
+      </c>
+      <c r="AN68" t="inlineStr">
+        <is>
+          <t>vandevenne2018</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AP68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>vandevenne2018_AAM_5.1_Sr</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>AAM_5.1</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>slag_blend</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Sr</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>leached_pct</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>milli_q_water</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>28</v>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="n">
+        <v>363.15</v>
+      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>synthetic_ca_si_al_slag</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>sodium_hydroxide</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AC69" t="inlineStr"/>
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="inlineStr"/>
+      <c r="AK69" t="inlineStr"/>
+      <c r="AL69" t="inlineStr"/>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>10.1016/j.jnucmat.2018.08.045</t>
+        </is>
+      </c>
+      <c r="AN69" t="inlineStr">
+        <is>
+          <t>vandevenne2018</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AP69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>jain2022_Cs2</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>FA-GP 2 wt% Cs</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>fly_ash_geopolymer</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Cs</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>2</v>
+      </c>
+      <c r="F70" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>leachability_index</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>deionised_water</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>fly_ash</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>sodium_hydroxide</t>
+        </is>
+      </c>
+      <c r="AA70" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="inlineStr"/>
+      <c r="AD70" t="inlineStr"/>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr"/>
+      <c r="AJ70" t="inlineStr"/>
+      <c r="AK70" t="inlineStr"/>
+      <c r="AL70" t="inlineStr"/>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>10.1016/j.cemconcomp.2022.104679</t>
+        </is>
+      </c>
+      <c r="AN70" t="inlineStr">
+        <is>
+          <t>jain2022</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AP70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>jain2022_Cs5</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>FA-GP 5 wt% Cs</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>fly_ash_geopolymer</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Cs</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>5</v>
+      </c>
+      <c r="F71" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>leachability_index</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>deionised_water</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>fly_ash</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>sodium_hydroxide</t>
+        </is>
+      </c>
+      <c r="AA71" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="inlineStr"/>
+      <c r="AD71" t="inlineStr"/>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr"/>
+      <c r="AJ71" t="inlineStr"/>
+      <c r="AK71" t="inlineStr"/>
+      <c r="AL71" t="inlineStr"/>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>10.1016/j.cemconcomp.2022.104679</t>
+        </is>
+      </c>
+      <c r="AN71" t="inlineStr">
+        <is>
+          <t>jain2022</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AP71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>jain2022_Cs8</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>FA-GP 8 wt% Cs</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>fly_ash_geopolymer</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Cs</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>8</v>
+      </c>
+      <c r="F72" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>leachability_index</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>deionised_water</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>fly_ash</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>sodium_hydroxide</t>
+        </is>
+      </c>
+      <c r="AA72" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr"/>
+      <c r="AL72" t="inlineStr"/>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>10.1016/j.cemconcomp.2022.104679</t>
+        </is>
+      </c>
+      <c r="AN72" t="inlineStr">
+        <is>
+          <t>jain2022</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AP72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>jain2022_Cs11</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>FA-GP 11 wt% Cs</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>fly_ash_geopolymer</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Cs</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>11</v>
+      </c>
+      <c r="F73" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>leachability_index</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>deionised_water</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>fly_ash</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>sodium_hydroxide</t>
+        </is>
+      </c>
+      <c r="AA73" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="inlineStr"/>
+      <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr"/>
+      <c r="AL73" t="inlineStr"/>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>10.1016/j.cemconcomp.2022.104679</t>
+        </is>
+      </c>
+      <c r="AN73" t="inlineStr">
+        <is>
+          <t>jain2022</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AP73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>jain2022_Cs20</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>FA-GP 20 wt% Cs</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>fly_ash_geopolymer</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Cs</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>20</v>
+      </c>
+      <c r="F74" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>leachability_index</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>deionised_water</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="n">
+        <v>40</v>
+      </c>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>fly_ash</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>sodium_hydroxide</t>
+        </is>
+      </c>
+      <c r="AA74" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="inlineStr"/>
+      <c r="AD74" t="inlineStr"/>
+      <c r="AE74" t="inlineStr"/>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="inlineStr"/>
+      <c r="AH74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr"/>
+      <c r="AJ74" t="inlineStr"/>
+      <c r="AK74" t="inlineStr"/>
+      <c r="AL74" t="inlineStr"/>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>10.1016/j.cemconcomp.2022.104679</t>
+        </is>
+      </c>
+      <c r="AN74" t="inlineStr">
+        <is>
+          <t>jain2022</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AP74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ74" t="b">
         <v>0</v>
       </c>
     </row>
